--- a/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -889,6 +889,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1006,6 +1009,9 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.version</t>
@@ -5755,7 +5761,7 @@
         <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>82</v>
@@ -5794,7 +5800,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5818,7 +5824,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5829,10 +5835,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5858,13 +5864,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5914,7 +5920,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5938,7 +5944,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5949,10 +5955,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5978,14 +5984,14 @@
         <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6034,7 +6040,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6058,7 +6064,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6069,10 +6075,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6098,14 +6104,14 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6154,7 +6160,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6178,7 +6184,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6189,10 +6195,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6215,19 +6221,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6276,7 +6282,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6300,7 +6306,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6311,13 +6317,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
@@ -6361,7 +6367,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6435,7 +6441,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>270</v>
@@ -6553,7 +6559,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6673,7 +6679,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>274</v>
@@ -6721,7 +6727,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -6760,7 +6766,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6784,7 +6790,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6795,10 +6801,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6824,13 +6830,13 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6880,7 +6886,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6904,7 +6910,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6915,10 +6921,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6944,14 +6950,14 @@
         <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7000,7 +7006,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7024,7 +7030,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7035,10 +7041,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7064,14 +7070,14 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7120,7 +7126,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7144,7 +7150,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7155,10 +7161,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7181,19 +7187,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7242,7 +7248,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7266,7 +7272,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7277,10 +7283,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7306,16 +7312,16 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7364,7 +7370,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7388,7 +7394,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7399,10 +7405,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7425,19 +7431,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7486,7 +7492,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7504,16 +7510,16 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7521,10 +7527,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7547,16 +7553,16 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7606,7 +7612,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7633,7 +7639,7 @@
         <v>253</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7641,14 +7647,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7667,19 +7673,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7728,7 +7734,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7746,16 +7752,16 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7763,14 +7769,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7789,19 +7795,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7850,7 +7856,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7865,19 +7871,19 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7885,10 +7891,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7914,13 +7920,13 @@
         <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7970,7 +7976,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7994,10 +8000,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8005,10 +8011,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8031,17 +8037,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8090,7 +8096,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8108,16 +8114,16 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8125,10 +8131,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8154,16 +8160,16 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8192,7 +8198,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8210,7 +8216,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8219,36 +8225,36 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8363,10 +8369,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8483,10 +8489,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8512,10 +8518,10 @@
         <v>146</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>261</v>
@@ -8605,10 +8611,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8723,10 +8729,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8843,10 +8849,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8930,7 +8936,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8954,7 +8960,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8965,10 +8971,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8994,13 +9000,13 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9050,7 +9056,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9074,7 +9080,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9085,10 +9091,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9114,14 +9120,14 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9170,7 +9176,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9194,7 +9200,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9205,10 +9211,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9234,14 +9240,14 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9290,7 +9296,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9314,7 +9320,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9325,10 +9331,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9351,19 +9357,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9412,7 +9418,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9436,7 +9442,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9447,10 +9453,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9476,16 +9482,16 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9534,7 +9540,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9558,7 +9564,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9569,10 +9575,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9598,16 +9604,16 @@
         <v>235</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9635,10 +9641,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9656,7 +9662,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9665,7 +9671,7 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9680,7 +9686,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9691,14 +9697,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9720,16 +9726,16 @@
         <v>235</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9757,10 +9763,10 @@
         <v>150</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9778,7 +9784,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9799,24 +9805,24 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9839,19 +9845,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9900,7 +9906,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9924,7 +9930,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9935,10 +9941,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9964,13 +9970,13 @@
         <v>235</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9999,10 +10005,10 @@
         <v>158</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10020,7 +10026,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10041,24 +10047,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10084,16 +10090,16 @@
         <v>235</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10121,10 +10127,10 @@
         <v>158</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10142,7 +10148,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10166,7 +10172,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10177,10 +10183,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10203,16 +10209,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10262,7 +10268,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10283,24 +10289,24 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10323,16 +10329,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10382,7 +10388,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10403,24 +10409,24 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10443,19 +10449,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10504,7 +10510,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10516,7 +10522,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10528,7 +10534,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10539,10 +10545,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10657,10 +10663,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10777,14 +10783,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10806,10 +10812,10 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>116</v>
@@ -10864,7 +10870,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10899,10 +10905,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10925,13 +10931,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10982,7 +10988,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10991,7 +10997,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11006,7 +11012,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11017,10 +11023,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11043,13 +11049,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11100,7 +11106,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11109,7 +11115,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11124,7 +11130,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11135,10 +11141,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11164,16 +11170,16 @@
         <v>235</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11201,10 +11207,10 @@
         <v>172</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11222,7 +11228,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11243,10 +11249,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11257,10 +11263,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11286,16 +11292,16 @@
         <v>235</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11323,10 +11329,10 @@
         <v>158</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11344,7 +11350,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11365,10 +11371,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11379,10 +11385,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11405,17 +11411,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11464,7 +11470,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11499,10 +11505,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11528,10 +11534,10 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11582,7 +11588,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11606,7 +11612,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11617,10 +11623,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11643,16 +11649,16 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11702,7 +11708,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11726,7 +11732,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11737,10 +11743,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11763,16 +11769,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11822,7 +11828,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11846,7 +11852,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -11857,10 +11863,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11883,19 +11889,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -11944,7 +11950,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11968,7 +11974,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -11979,10 +11985,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12097,10 +12103,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12217,14 +12223,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12246,10 +12252,10 @@
         <v>113</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>116</v>
@@ -12304,7 +12310,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12339,10 +12345,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12368,13 +12374,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>248</v>
@@ -12426,7 +12432,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>93</v>
@@ -12447,7 +12453,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>253</v>
@@ -12461,10 +12467,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12487,19 +12493,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12548,7 +12554,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12569,24 +12575,24 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12612,16 +12618,16 @@
         <v>235</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12649,10 +12655,10 @@
         <v>150</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12670,7 +12676,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12679,7 +12685,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -12694,7 +12700,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12705,14 +12711,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12734,16 +12740,16 @@
         <v>235</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12771,10 +12777,10 @@
         <v>150</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12792,7 +12798,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12813,24 +12819,24 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12856,16 +12862,16 @@
         <v>83</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -12914,7 +12920,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12938,7 +12944,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>

--- a/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-prostate-gleason-grade-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
